--- a/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAC3E614-E8AF-4C24-B908-C0DB54D9295E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCFECD7-A6D2-4098-8328-6E560A821395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="23025" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -217,21 +217,6 @@
     <t>${competition.federationWebSite}</t>
   </si>
   <si>
-    <t>${session.timeKeeper}</t>
-  </si>
-  <si>
-    <t>${session.referee1}</t>
-  </si>
-  <si>
-    <t>${session.referee2}</t>
-  </si>
-  <si>
-    <t>${session.referee3}</t>
-  </si>
-  <si>
-    <t>${session.announcer}</t>
-  </si>
-  <si>
     <t>${competition.competitionSite}</t>
   </si>
   <si>
@@ -376,18 +361,9 @@
     <t>${t.get("Results.RecordDate")}</t>
   </si>
   <si>
-    <t>${session.marshall} ${session.marshal2}</t>
-  </si>
-  <si>
     <t>${t.get("JuryPresident")}</t>
   </si>
   <si>
-    <t>${session.jury2} ${session.jury3} ${session.jury4} ${session.jury5}</t>
-  </si>
-  <si>
-    <t>${session.jury1}</t>
-  </si>
-  <si>
     <t>${t.get("Results.RecordAgeGroup")}</t>
   </si>
   <si>
@@ -409,9 +385,6 @@
     <t>${r.resRecordLift}</t>
   </si>
   <si>
-    <t>${session.technicalController} ${session.technicalController2}</t>
-  </si>
-  <si>
     <t>${l.totalRank &lt; 0 ? "inv." : (l.totalRank &gt; 0 ? l.totalRank : "" )}</t>
   </si>
   <si>
@@ -434,6 +407,33 @@
   </si>
   <si>
     <t>${l.categoryScoreRank &lt; 0 ? t.get("Results.Extra/Invited") : (l.categoryScoreRank &gt; 0 ? l.categoryScoreRank : "" )}</t>
+  </si>
+  <si>
+    <t>${session.announcerAsTO} ${session.referee1AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.marshallAsTO} ${session.marshallAsTO.federationId} ${session.marshal2AsTO} ${session.marshal2AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.timeKeeperAsTO} ${session.timeKeeperAsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.technicalControllerAsTO} ${session.technicalControllerAsTO.federationId} ${session.technicalController2AsTO} ${session.technicalController2AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.referee1AsTO} ${session.referee1AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.referee2AsTO} ${session.referee2AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.referee3AsTO} ${session.referee3AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.jury1AsTO} ${session.jury1AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.jury2AsTO} ${session.jury2AsTO.federationId} ${session.jury3AsTO} ${session.jury3AsTO.federationId} ${session.jury4AsTO} ${session.jury4AsTO.federationId} ${session.jury5AsTO} ${session.jury5AsTO.federationId}</t>
   </si>
 </sst>
 </file>
@@ -1027,7 +1027,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1296,14 +1296,64 @@
     <xf numFmtId="1" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1319,56 +1369,11 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent1" xfId="1" builtinId="29" customBuiltin="1"/>
@@ -1884,22 +1889,22 @@
       <c r="F1" s="49"/>
       <c r="G1" s="15"/>
       <c r="J1" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="K1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
-      <c r="V1" s="108"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
     </row>
     <row r="2" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="52" t="s">
@@ -1908,10 +1913,10 @@
       <c r="B2" s="53"/>
       <c r="C2" s="4"/>
       <c r="J2" s="32" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K2" s="54" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L2" s="95"/>
       <c r="M2" s="55"/>
@@ -1920,7 +1925,7 @@
       <c r="P2" s="56"/>
       <c r="Q2" s="57"/>
       <c r="R2" s="32" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S2" t="s">
         <v>18</v>
@@ -1933,19 +1938,19 @@
       </c>
       <c r="B3" s="59"/>
       <c r="J3" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" s="105" t="s">
-        <v>62</v>
-      </c>
-      <c r="L3" s="105"/>
-      <c r="M3" s="105"/>
-      <c r="N3" s="105"/>
-      <c r="O3" s="105"/>
+        <v>29</v>
+      </c>
+      <c r="K3" s="119" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" s="119"/>
+      <c r="M3" s="119"/>
+      <c r="N3" s="119"/>
+      <c r="O3" s="119"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="60"/>
       <c r="R3" s="32" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="S3" s="61" t="s">
         <v>19</v>
@@ -1956,17 +1961,17 @@
     </row>
     <row r="4" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="58" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B4" s="58"/>
       <c r="C4" s="48"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="J4" s="32" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K4" s="97" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="L4"/>
       <c r="M4" s="3"/>
@@ -1983,64 +1988,64 @@
       <c r="H6" s="7"/>
       <c r="I6" s="9"/>
       <c r="J6" s="7"/>
-      <c r="K6" s="101" t="s">
+      <c r="K6" s="108" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="109"/>
+      <c r="M6" s="110"/>
+      <c r="N6" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="114"/>
-      <c r="M6" s="102"/>
-      <c r="N6" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="O6" s="101" t="s">
-        <v>44</v>
-      </c>
-      <c r="P6" s="114"/>
-      <c r="Q6" s="102"/>
+      <c r="O6" s="108" t="s">
+        <v>39</v>
+      </c>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="110"/>
       <c r="R6" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="S6" s="111" t="s">
-        <v>50</v>
-      </c>
-      <c r="T6" s="109" t="s">
-        <v>51</v>
-      </c>
-      <c r="U6" s="115" t="s">
-        <v>91</v>
-      </c>
-      <c r="V6" s="117" t="s">
-        <v>92</v>
+        <v>43</v>
+      </c>
+      <c r="S6" s="105" t="s">
+        <v>45</v>
+      </c>
+      <c r="T6" s="103" t="s">
+        <v>46</v>
+      </c>
+      <c r="U6" s="111" t="s">
+        <v>82</v>
+      </c>
+      <c r="V6" s="113" t="s">
+        <v>83</v>
       </c>
       <c r="X6"/>
     </row>
     <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="108" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="110"/>
+      <c r="G7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>37</v>
-      </c>
-      <c r="E7" s="101" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="102"/>
-      <c r="G7" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>42</v>
       </c>
       <c r="K7" s="10">
         <v>1</v>
@@ -2052,7 +2057,7 @@
         <v>3</v>
       </c>
       <c r="N7" s="43" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O7" s="10">
         <v>1</v>
@@ -2064,12 +2069,12 @@
         <v>3</v>
       </c>
       <c r="R7" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="S7" s="112"/>
-      <c r="T7" s="110"/>
-      <c r="U7" s="116"/>
-      <c r="V7" s="118"/>
+        <v>55</v>
+      </c>
+      <c r="S7" s="106"/>
+      <c r="T7" s="104"/>
+      <c r="U7" s="112"/>
+      <c r="V7" s="114"/>
     </row>
     <row r="8" spans="1:24" s="28" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="67"/>
@@ -2087,7 +2092,7 @@
     </row>
     <row r="9" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="70" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B9" s="71"/>
       <c r="C9" s="72"/>
@@ -2108,10 +2113,10 @@
       <c r="R9" s="72"/>
       <c r="S9" s="72"/>
       <c r="T9" s="72"/>
-      <c r="U9" s="119" t="s">
-        <v>93</v>
-      </c>
-      <c r="V9" s="120"/>
+      <c r="U9" s="115" t="s">
+        <v>84</v>
+      </c>
+      <c r="V9" s="116"/>
       <c r="X9"/>
     </row>
     <row r="10" spans="1:24" s="28" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -2119,7 +2124,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>1</v>
@@ -2127,10 +2132,10 @@
       <c r="D10" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="103" t="s">
+      <c r="E10" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="104"/>
+      <c r="F10" s="118"/>
       <c r="G10" s="65" t="s">
         <v>5</v>
       </c>
@@ -2141,7 +2146,7 @@
         <v>6</v>
       </c>
       <c r="J10" s="64" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K10" s="27" t="s">
         <v>10</v>
@@ -2171,13 +2176,13 @@
         <v>7</v>
       </c>
       <c r="T10" s="46" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="U10" s="99" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="V10" s="100" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2200,7 +2205,7 @@
     </row>
     <row r="12" spans="1:24" s="49" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="49" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J12" s="50"/>
     </row>
@@ -2230,94 +2235,94 @@
     </row>
     <row r="14" spans="1:24" s="92" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A14" s="83" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B14" s="84"/>
       <c r="C14" s="85"/>
       <c r="D14" s="86" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E14" s="87" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F14" s="86" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G14" s="88" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H14" s="89"/>
       <c r="I14" s="86" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J14" s="83" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="K14" s="90"/>
       <c r="L14" s="84"/>
       <c r="M14" s="85"/>
       <c r="N14" s="83" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="O14" s="84"/>
       <c r="P14" s="91"/>
       <c r="Q14" s="83" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="R14" s="84"/>
       <c r="S14" s="83" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="T14" s="90"/>
       <c r="U14" s="83" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="V14" s="91"/>
       <c r="X14" s="85"/>
     </row>
     <row r="15" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="75" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B15" s="76"/>
       <c r="C15" s="77"/>
       <c r="D15" s="78" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E15" s="79" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F15" s="94" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G15" s="79" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H15" s="77"/>
       <c r="I15" s="93" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J15" s="79" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K15" s="76"/>
       <c r="L15" s="76"/>
       <c r="M15" s="77"/>
       <c r="N15" s="79" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="O15" s="76"/>
       <c r="P15" s="77"/>
       <c r="Q15" s="75" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="R15" s="76"/>
       <c r="S15" s="82" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="T15" s="76"/>
       <c r="U15" s="81" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="V15" s="77"/>
       <c r="X15" s="77"/>
@@ -2326,23 +2331,23 @@
       <c r="A16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
-      <c r="E16" s="106" t="s">
-        <v>53</v>
+      <c r="E16" s="120" t="s">
+        <v>48</v>
       </c>
       <c r="G16" s="24"/>
       <c r="H16" s="15"/>
       <c r="I16" s="14"/>
-      <c r="J16" s="107" t="s">
-        <v>54</v>
-      </c>
-      <c r="K16" s="107"/>
+      <c r="J16" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="102"/>
       <c r="L16" s="14"/>
       <c r="N16" s="16"/>
       <c r="P16" s="14"/>
-      <c r="Q16" s="113" t="s">
-        <v>55</v>
-      </c>
-      <c r="R16" s="113"/>
+      <c r="Q16" s="107" t="s">
+        <v>50</v>
+      </c>
+      <c r="R16" s="107"/>
       <c r="S16" s="47"/>
       <c r="T16" s="14"/>
       <c r="U16" s="12"/>
@@ -2355,38 +2360,40 @@
     <row r="17" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="35" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="D17" s="17"/>
-      <c r="E17" s="106"/>
+      <c r="E17" s="120"/>
       <c r="F17" s="41" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G17" s="17"/>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
-      <c r="J17" s="107"/>
-      <c r="K17" s="107"/>
+      <c r="J17" s="102"/>
+      <c r="K17" s="102"/>
       <c r="L17" s="41" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="M17" s="17"/>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
       <c r="P17" s="19"/>
-      <c r="Q17" s="113"/>
-      <c r="R17" s="113"/>
+      <c r="Q17" s="107"/>
+      <c r="R17" s="107"/>
       <c r="S17" s="41" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="T17" s="19"/>
+      <c r="U17" s="17"/>
+      <c r="V17" s="121"/>
       <c r="W17"/>
       <c r="X17" s="17"/>
     </row>
-    <row r="18" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" s="20" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A18" s="21"/>
       <c r="B18" s="33"/>
       <c r="D18" s="37"/>
@@ -2403,8 +2410,8 @@
       <c r="Q18" s="21"/>
       <c r="S18" s="37"/>
       <c r="T18" s="37"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
+      <c r="U18" s="37"/>
+      <c r="V18" s="122"/>
       <c r="X18" s="37"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
@@ -2414,45 +2421,49 @@
       <c r="E19" s="30"/>
       <c r="F19" s="14"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="107" t="s">
-        <v>58</v>
-      </c>
-      <c r="K19" s="107"/>
+      <c r="J19" s="102" t="s">
+        <v>53</v>
+      </c>
+      <c r="K19" s="102"/>
       <c r="M19"/>
       <c r="N19" s="1"/>
       <c r="O19" s="12"/>
       <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19" s="123"/>
       <c r="W19"/>
       <c r="X19"/>
     </row>
     <row r="20" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="35" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="35" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F20" s="41" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
-      <c r="J20" s="107"/>
-      <c r="K20" s="107"/>
+      <c r="J20" s="102"/>
+      <c r="K20" s="102"/>
       <c r="L20" s="41" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="M20" s="19"/>
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
       <c r="P20" s="17"/>
       <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20" s="123"/>
       <c r="W20"/>
       <c r="X20"/>
     </row>
@@ -2471,8 +2482,7 @@
       <c r="O21" s="37"/>
       <c r="P21" s="37"/>
       <c r="Q21" s="21"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
+      <c r="V21" s="122"/>
       <c r="X21" s="37"/>
     </row>
     <row r="22" spans="1:24" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -2488,23 +2498,25 @@
       <c r="N22" s="1"/>
       <c r="O22" s="12"/>
       <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22" s="123"/>
       <c r="W22"/>
       <c r="X22"/>
     </row>
     <row r="23" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="35" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="35" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F23" s="41" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
@@ -2516,6 +2528,8 @@
       <c r="N23" s="17"/>
       <c r="O23" s="17"/>
       <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23" s="123"/>
       <c r="W23"/>
       <c r="X23"/>
     </row>
@@ -2855,6 +2869,11 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="15">
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="K3:O3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="J16:K17"/>
     <mergeCell ref="K1:V1"/>
     <mergeCell ref="J19:K20"/>
     <mergeCell ref="T6:T7"/>
@@ -2865,11 +2884,6 @@
     <mergeCell ref="U6:U7"/>
     <mergeCell ref="V6:V7"/>
     <mergeCell ref="U9:V9"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="K3:O3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="J16:K17"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:D8">
     <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">
@@ -2887,7 +2901,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation showErrorMessage="1" sqref="F23 F20 C20 C17 S17 L17 F17 L20 C23 K4" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 C17 S17 L17 F17 F20 C23 L20" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="G16 H11:H13" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>

--- a/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCFECD7-A6D2-4098-8328-6E560A821395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56AA30C7-9E8A-4A69-A268-B71D83F53287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27225" yWindow="4995" windowWidth="24615" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -409,9 +409,6 @@
     <t>${l.categoryScoreRank &lt; 0 ? t.get("Results.Extra/Invited") : (l.categoryScoreRank &gt; 0 ? l.categoryScoreRank : "" )}</t>
   </si>
   <si>
-    <t>${session.announcerAsTO} ${session.referee1AsTO.federationId}</t>
-  </si>
-  <si>
     <t>${session.marshallAsTO} ${session.marshallAsTO.federationId} ${session.marshal2AsTO} ${session.marshal2AsTO.federationId}</t>
   </si>
   <si>
@@ -434,6 +431,9 @@
   </si>
   <si>
     <t>${session.jury2AsTO} ${session.jury2AsTO.federationId} ${session.jury3AsTO} ${session.jury3AsTO.federationId} ${session.jury4AsTO} ${session.jury4AsTO.federationId} ${session.jury5AsTO} ${session.jury5AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.announcerAsTO} ${session.announcerAsTO.federationId}</t>
   </si>
 </sst>
 </file>
@@ -1296,13 +1296,41 @@
     <xf numFmtId="1" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1320,18 +1348,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1354,26 +1374,6 @@
     <xf numFmtId="0" fontId="26" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent1" xfId="1" builtinId="29" customBuiltin="1"/>
@@ -1891,20 +1891,20 @@
       <c r="J1" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="101" t="s">
+      <c r="K1" s="111" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="101"/>
-      <c r="T1" s="101"/>
-      <c r="U1" s="101"/>
-      <c r="V1" s="101"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
+      <c r="V1" s="111"/>
     </row>
     <row r="2" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="52" t="s">
@@ -1940,13 +1940,13 @@
       <c r="J3" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="119" t="s">
+      <c r="K3" s="108" t="s">
         <v>57</v>
       </c>
-      <c r="L3" s="119"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="119"/>
-      <c r="O3" s="119"/>
+      <c r="L3" s="108"/>
+      <c r="M3" s="108"/>
+      <c r="N3" s="108"/>
+      <c r="O3" s="108"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="60"/>
       <c r="R3" s="32" t="s">
@@ -1988,32 +1988,32 @@
       <c r="H6" s="7"/>
       <c r="I6" s="9"/>
       <c r="J6" s="7"/>
-      <c r="K6" s="108" t="s">
+      <c r="K6" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="109"/>
-      <c r="M6" s="110"/>
+      <c r="L6" s="117"/>
+      <c r="M6" s="105"/>
       <c r="N6" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="108" t="s">
+      <c r="O6" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="P6" s="109"/>
-      <c r="Q6" s="110"/>
+      <c r="P6" s="117"/>
+      <c r="Q6" s="105"/>
       <c r="R6" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="S6" s="105" t="s">
+      <c r="S6" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="T6" s="103" t="s">
+      <c r="T6" s="112" t="s">
         <v>46</v>
       </c>
-      <c r="U6" s="111" t="s">
+      <c r="U6" s="118" t="s">
         <v>82</v>
       </c>
-      <c r="V6" s="113" t="s">
+      <c r="V6" s="120" t="s">
         <v>83</v>
       </c>
       <c r="X6"/>
@@ -2031,10 +2031,10 @@
       <c r="D7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="108" t="s">
+      <c r="E7" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="110"/>
+      <c r="F7" s="105"/>
       <c r="G7" s="11" t="s">
         <v>34</v>
       </c>
@@ -2071,10 +2071,10 @@
       <c r="R7" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="S7" s="106"/>
-      <c r="T7" s="104"/>
-      <c r="U7" s="112"/>
-      <c r="V7" s="114"/>
+      <c r="S7" s="115"/>
+      <c r="T7" s="113"/>
+      <c r="U7" s="119"/>
+      <c r="V7" s="121"/>
     </row>
     <row r="8" spans="1:24" s="28" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="67"/>
@@ -2113,10 +2113,10 @@
       <c r="R9" s="72"/>
       <c r="S9" s="72"/>
       <c r="T9" s="72"/>
-      <c r="U9" s="115" t="s">
+      <c r="U9" s="122" t="s">
         <v>84</v>
       </c>
-      <c r="V9" s="116"/>
+      <c r="V9" s="123"/>
       <c r="X9"/>
     </row>
     <row r="10" spans="1:24" s="28" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -2132,10 +2132,10 @@
       <c r="D10" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="117" t="s">
+      <c r="E10" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="118"/>
+      <c r="F10" s="107"/>
       <c r="G10" s="65" t="s">
         <v>5</v>
       </c>
@@ -2331,23 +2331,23 @@
       <c r="A16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
-      <c r="E16" s="120" t="s">
+      <c r="E16" s="109" t="s">
         <v>48</v>
       </c>
       <c r="G16" s="24"/>
       <c r="H16" s="15"/>
       <c r="I16" s="14"/>
-      <c r="J16" s="102" t="s">
+      <c r="J16" s="110" t="s">
         <v>49</v>
       </c>
-      <c r="K16" s="102"/>
+      <c r="K16" s="110"/>
       <c r="L16" s="14"/>
       <c r="N16" s="16"/>
       <c r="P16" s="14"/>
-      <c r="Q16" s="107" t="s">
+      <c r="Q16" s="116" t="s">
         <v>50</v>
       </c>
-      <c r="R16" s="107"/>
+      <c r="R16" s="116"/>
       <c r="S16" s="47"/>
       <c r="T16" s="14"/>
       <c r="U16" s="12"/>
@@ -2363,33 +2363,33 @@
         <v>47</v>
       </c>
       <c r="C17" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="109"/>
+      <c r="F17" s="41" t="s">
         <v>87</v>
-      </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="120"/>
-      <c r="F17" s="41" t="s">
-        <v>88</v>
       </c>
       <c r="G17" s="17"/>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
-      <c r="J17" s="102"/>
-      <c r="K17" s="102"/>
+      <c r="J17" s="110"/>
+      <c r="K17" s="110"/>
       <c r="L17" s="41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M17" s="17"/>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
       <c r="P17" s="19"/>
-      <c r="Q17" s="107"/>
-      <c r="R17" s="107"/>
+      <c r="Q17" s="116"/>
+      <c r="R17" s="116"/>
       <c r="S17" s="41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T17" s="19"/>
       <c r="U17" s="17"/>
-      <c r="V17" s="121"/>
+      <c r="V17" s="101"/>
       <c r="W17"/>
       <c r="X17" s="17"/>
     </row>
@@ -2411,7 +2411,7 @@
       <c r="S18" s="37"/>
       <c r="T18" s="37"/>
       <c r="U18" s="37"/>
-      <c r="V18" s="122"/>
+      <c r="V18" s="102"/>
       <c r="X18" s="37"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
@@ -2421,16 +2421,16 @@
       <c r="E19" s="30"/>
       <c r="F19" s="14"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="102" t="s">
+      <c r="J19" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="K19" s="102"/>
+      <c r="K19" s="110"/>
       <c r="M19"/>
       <c r="N19" s="1"/>
       <c r="O19" s="12"/>
       <c r="T19"/>
       <c r="U19"/>
-      <c r="V19" s="123"/>
+      <c r="V19" s="103"/>
       <c r="W19"/>
       <c r="X19"/>
     </row>
@@ -2440,22 +2440,22 @@
         <v>51</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="35" t="s">
         <v>52</v>
       </c>
       <c r="F20" s="41" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
-      <c r="J20" s="102"/>
-      <c r="K20" s="102"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
       <c r="L20" s="41" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M20" s="19"/>
       <c r="N20" s="17"/>
@@ -2463,7 +2463,7 @@
       <c r="P20" s="17"/>
       <c r="T20"/>
       <c r="U20"/>
-      <c r="V20" s="123"/>
+      <c r="V20" s="103"/>
       <c r="W20"/>
       <c r="X20"/>
     </row>
@@ -2482,7 +2482,7 @@
       <c r="O21" s="37"/>
       <c r="P21" s="37"/>
       <c r="Q21" s="21"/>
-      <c r="V21" s="122"/>
+      <c r="V21" s="102"/>
       <c r="X21" s="37"/>
     </row>
     <row r="22" spans="1:24" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -2499,7 +2499,7 @@
       <c r="O22" s="12"/>
       <c r="T22"/>
       <c r="U22"/>
-      <c r="V22" s="123"/>
+      <c r="V22" s="103"/>
       <c r="W22"/>
       <c r="X22"/>
     </row>
@@ -2509,14 +2509,14 @@
         <v>71</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="35" t="s">
         <v>54</v>
       </c>
       <c r="F23" s="41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
@@ -2529,7 +2529,7 @@
       <c r="O23" s="17"/>
       <c r="T23"/>
       <c r="U23"/>
-      <c r="V23" s="123"/>
+      <c r="V23" s="103"/>
       <c r="W23"/>
       <c r="X23"/>
     </row>
@@ -2869,11 +2869,6 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="15">
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="K3:O3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="J16:K17"/>
     <mergeCell ref="K1:V1"/>
     <mergeCell ref="J19:K20"/>
     <mergeCell ref="T6:T7"/>
@@ -2884,6 +2879,11 @@
     <mergeCell ref="U6:U7"/>
     <mergeCell ref="V6:V7"/>
     <mergeCell ref="U9:V9"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="K3:O3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="J16:K17"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:D8">
     <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">

--- a/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\protocol\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56AA30C7-9E8A-4A69-A268-B71D83F53287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB637FE4-08A8-42F7-8817-4D0AD0DDE20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27225" yWindow="4995" windowWidth="24615" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="5295" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="98">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -430,10 +430,16 @@
     <t>${session.jury1AsTO} ${session.jury1AsTO.federationId}</t>
   </si>
   <si>
-    <t>${session.jury2AsTO} ${session.jury2AsTO.federationId} ${session.jury3AsTO} ${session.jury3AsTO.federationId} ${session.jury4AsTO} ${session.jury4AsTO.federationId} ${session.jury5AsTO} ${session.jury5AsTO.federationId}</t>
-  </si>
-  <si>
     <t>${session.announcerAsTO} ${session.announcerAsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${t.get("Reserve")}</t>
+  </si>
+  <si>
+    <t>${session.reserveAsTO} ${session.reserveAsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.jury2AsTO} ${session.jury2AsTO.federationId} ${session.jury3AsTO} ${session.jury3AsTO.federationId} ${session.jury4AsTO} ${session.jury4AsTO.federationId} ${session.jury5AsTO} ${session.jury5AsTO.federationId} ${session.reserveJuryAsTO != null ? "("+t.get("Reserve")+") "+session.reserveJuryAsTO+" "+session.reserveJuryAsTO.federationId : ""}</t>
   </si>
 </sst>
 </file>
@@ -1027,7 +1033,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1301,14 +1307,64 @@
     </xf>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1324,56 +1380,11 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent1" xfId="1" builtinId="29" customBuiltin="1"/>
@@ -1891,20 +1902,20 @@
       <c r="J1" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="111" t="s">
+      <c r="K1" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
-      <c r="V1" s="111"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="104"/>
+      <c r="O1" s="104"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="104"/>
+      <c r="T1" s="104"/>
+      <c r="U1" s="104"/>
+      <c r="V1" s="104"/>
     </row>
     <row r="2" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="52" t="s">
@@ -1940,13 +1951,13 @@
       <c r="J3" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="108" t="s">
+      <c r="K3" s="122" t="s">
         <v>57</v>
       </c>
-      <c r="L3" s="108"/>
-      <c r="M3" s="108"/>
-      <c r="N3" s="108"/>
-      <c r="O3" s="108"/>
+      <c r="L3" s="122"/>
+      <c r="M3" s="122"/>
+      <c r="N3" s="122"/>
+      <c r="O3" s="122"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="60"/>
       <c r="R3" s="32" t="s">
@@ -1988,32 +1999,32 @@
       <c r="H6" s="7"/>
       <c r="I6" s="9"/>
       <c r="J6" s="7"/>
-      <c r="K6" s="104" t="s">
+      <c r="K6" s="111" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="117"/>
-      <c r="M6" s="105"/>
+      <c r="L6" s="112"/>
+      <c r="M6" s="113"/>
       <c r="N6" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="104" t="s">
+      <c r="O6" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="P6" s="117"/>
-      <c r="Q6" s="105"/>
+      <c r="P6" s="112"/>
+      <c r="Q6" s="113"/>
       <c r="R6" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="S6" s="114" t="s">
+      <c r="S6" s="108" t="s">
         <v>45</v>
       </c>
-      <c r="T6" s="112" t="s">
+      <c r="T6" s="106" t="s">
         <v>46</v>
       </c>
-      <c r="U6" s="118" t="s">
+      <c r="U6" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="V6" s="120" t="s">
+      <c r="V6" s="116" t="s">
         <v>83</v>
       </c>
       <c r="X6"/>
@@ -2031,10 +2042,10 @@
       <c r="D7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="104" t="s">
+      <c r="E7" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="105"/>
+      <c r="F7" s="113"/>
       <c r="G7" s="11" t="s">
         <v>34</v>
       </c>
@@ -2071,10 +2082,10 @@
       <c r="R7" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="S7" s="115"/>
-      <c r="T7" s="113"/>
-      <c r="U7" s="119"/>
-      <c r="V7" s="121"/>
+      <c r="S7" s="109"/>
+      <c r="T7" s="107"/>
+      <c r="U7" s="115"/>
+      <c r="V7" s="117"/>
     </row>
     <row r="8" spans="1:24" s="28" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="67"/>
@@ -2113,10 +2124,10 @@
       <c r="R9" s="72"/>
       <c r="S9" s="72"/>
       <c r="T9" s="72"/>
-      <c r="U9" s="122" t="s">
+      <c r="U9" s="118" t="s">
         <v>84</v>
       </c>
-      <c r="V9" s="123"/>
+      <c r="V9" s="119"/>
       <c r="X9"/>
     </row>
     <row r="10" spans="1:24" s="28" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -2132,10 +2143,10 @@
       <c r="D10" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="106" t="s">
+      <c r="E10" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="107"/>
+      <c r="F10" s="121"/>
       <c r="G10" s="65" t="s">
         <v>5</v>
       </c>
@@ -2331,23 +2342,23 @@
       <c r="A16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
-      <c r="E16" s="109" t="s">
+      <c r="E16" s="123" t="s">
         <v>48</v>
       </c>
       <c r="G16" s="24"/>
       <c r="H16" s="15"/>
       <c r="I16" s="14"/>
-      <c r="J16" s="110" t="s">
+      <c r="J16" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="K16" s="110"/>
+      <c r="K16" s="105"/>
       <c r="L16" s="14"/>
       <c r="N16" s="16"/>
       <c r="P16" s="14"/>
-      <c r="Q16" s="116" t="s">
+      <c r="Q16" s="110" t="s">
         <v>50</v>
       </c>
-      <c r="R16" s="116"/>
+      <c r="R16" s="110"/>
       <c r="S16" s="47"/>
       <c r="T16" s="14"/>
       <c r="U16" s="12"/>
@@ -2363,18 +2374,18 @@
         <v>47</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D17" s="17"/>
-      <c r="E17" s="109"/>
+      <c r="E17" s="123"/>
       <c r="F17" s="41" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="17"/>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
-      <c r="J17" s="110"/>
-      <c r="K17" s="110"/>
+      <c r="J17" s="105"/>
+      <c r="K17" s="105"/>
       <c r="L17" s="41" t="s">
         <v>88</v>
       </c>
@@ -2382,8 +2393,8 @@
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
       <c r="P17" s="19"/>
-      <c r="Q17" s="116"/>
-      <c r="R17" s="116"/>
+      <c r="Q17" s="110"/>
+      <c r="R17" s="110"/>
       <c r="S17" s="41" t="s">
         <v>89</v>
       </c>
@@ -2391,7 +2402,6 @@
       <c r="U17" s="17"/>
       <c r="V17" s="101"/>
       <c r="W17"/>
-      <c r="X17" s="17"/>
     </row>
     <row r="18" spans="1:24" s="20" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A18" s="21"/>
@@ -2412,7 +2422,6 @@
       <c r="T18" s="37"/>
       <c r="U18" s="37"/>
       <c r="V18" s="102"/>
-      <c r="X18" s="37"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
@@ -2421,17 +2430,20 @@
       <c r="E19" s="30"/>
       <c r="F19" s="14"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="110" t="s">
+      <c r="J19" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="K19" s="110"/>
+      <c r="K19" s="105"/>
       <c r="M19"/>
       <c r="N19" s="1"/>
       <c r="O19" s="12"/>
+      <c r="Q19" s="105" t="s">
+        <v>95</v>
+      </c>
+      <c r="R19" s="105"/>
+      <c r="S19" s="1"/>
       <c r="T19"/>
-      <c r="U19"/>
-      <c r="V19" s="103"/>
-      <c r="W19"/>
+      <c r="V19" s="12"/>
       <c r="X19"/>
     </row>
     <row r="20" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2452,8 +2464,8 @@
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="105"/>
       <c r="L20" s="41" t="s">
         <v>92</v>
       </c>
@@ -2461,10 +2473,14 @@
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
       <c r="P20" s="17"/>
-      <c r="T20"/>
-      <c r="U20"/>
-      <c r="V20" s="103"/>
-      <c r="W20"/>
+      <c r="Q20" s="105"/>
+      <c r="R20" s="105"/>
+      <c r="S20" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="T20" s="19"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
       <c r="X20"/>
     </row>
     <row r="21" spans="1:24" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2483,7 +2499,6 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="21"/>
       <c r="V21" s="102"/>
-      <c r="X21" s="37"/>
     </row>
     <row r="22" spans="1:24" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
@@ -2516,7 +2531,7 @@
         <v>54</v>
       </c>
       <c r="F23" s="41" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
@@ -2526,10 +2541,14 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="T23"/>
-      <c r="U23"/>
-      <c r="V23" s="103"/>
+      <c r="O23" s="124"/>
+      <c r="P23" s="124"/>
+      <c r="Q23" s="124"/>
+      <c r="R23" s="124"/>
+      <c r="S23" s="125"/>
+      <c r="T23" s="125"/>
+      <c r="U23" s="125"/>
+      <c r="V23" s="126"/>
       <c r="W23"/>
       <c r="X23"/>
     </row>
@@ -2868,7 +2887,12 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="K3:O3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="J16:K17"/>
     <mergeCell ref="K1:V1"/>
     <mergeCell ref="J19:K20"/>
     <mergeCell ref="T6:T7"/>
@@ -2879,11 +2903,7 @@
     <mergeCell ref="U6:U7"/>
     <mergeCell ref="V6:V7"/>
     <mergeCell ref="U9:V9"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="K3:O3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="J16:K17"/>
+    <mergeCell ref="Q19:R20"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:D8">
     <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">
@@ -2901,7 +2921,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 C17 S17 L17 F17 F20 C23 L20" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="G16 H11:H13" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>

--- a/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\protocol\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB637FE4-08A8-42F7-8817-4D0AD0DDE20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43445A5B-31BE-4C28-A043-812C2C384D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5295" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5970" yWindow="5010" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="100">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -439,7 +439,13 @@
     <t>${session.reserveAsTO} ${session.reserveAsTO.federationId}</t>
   </si>
   <si>
-    <t>${session.jury2AsTO} ${session.jury2AsTO.federationId} ${session.jury3AsTO} ${session.jury3AsTO.federationId} ${session.jury4AsTO} ${session.jury4AsTO.federationId} ${session.jury5AsTO} ${session.jury5AsTO.federationId} ${session.reserveJuryAsTO != null ? "("+t.get("Reserve")+") "+session.reserveJuryAsTO+" "+session.reserveJuryAsTO.federationId : ""}</t>
+    <t>${t.get("ReserveJury")}</t>
+  </si>
+  <si>
+    <t>${session.jury2AsTO} ${session.jury2AsTO.federationId} ${session.jury3AsTO} ${session.jury3AsTO.federationId} ${session.jury4AsTO} ${session.jury4AsTO.federationId} ${session.jury5AsTO} ${session.jury5AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.reserveJuryAsTO} ${session.reserveJuryAsTO.federationId}</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1039,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1306,14 +1312,40 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1331,18 +1363,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1365,26 +1389,6 @@
     <xf numFmtId="0" fontId="26" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent1" xfId="1" builtinId="29" customBuiltin="1"/>
@@ -1902,20 +1906,20 @@
       <c r="J1" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="104" t="s">
+      <c r="K1" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
-      <c r="N1" s="104"/>
-      <c r="O1" s="104"/>
-      <c r="P1" s="104"/>
-      <c r="Q1" s="104"/>
-      <c r="R1" s="104"/>
-      <c r="S1" s="104"/>
-      <c r="T1" s="104"/>
-      <c r="U1" s="104"/>
-      <c r="V1" s="104"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
+      <c r="V1" s="112"/>
     </row>
     <row r="2" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="52" t="s">
@@ -1951,13 +1955,13 @@
       <c r="J3" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="109" t="s">
         <v>57</v>
       </c>
-      <c r="L3" s="122"/>
-      <c r="M3" s="122"/>
-      <c r="N3" s="122"/>
-      <c r="O3" s="122"/>
+      <c r="L3" s="109"/>
+      <c r="M3" s="109"/>
+      <c r="N3" s="109"/>
+      <c r="O3" s="109"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="60"/>
       <c r="R3" s="32" t="s">
@@ -1999,32 +2003,32 @@
       <c r="H6" s="7"/>
       <c r="I6" s="9"/>
       <c r="J6" s="7"/>
-      <c r="K6" s="111" t="s">
+      <c r="K6" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="112"/>
-      <c r="M6" s="113"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="106"/>
       <c r="N6" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="111" t="s">
+      <c r="O6" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="P6" s="112"/>
-      <c r="Q6" s="113"/>
+      <c r="P6" s="118"/>
+      <c r="Q6" s="106"/>
       <c r="R6" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="S6" s="108" t="s">
+      <c r="S6" s="115" t="s">
         <v>45</v>
       </c>
-      <c r="T6" s="106" t="s">
+      <c r="T6" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="U6" s="114" t="s">
+      <c r="U6" s="119" t="s">
         <v>82</v>
       </c>
-      <c r="V6" s="116" t="s">
+      <c r="V6" s="121" t="s">
         <v>83</v>
       </c>
       <c r="X6"/>
@@ -2042,10 +2046,10 @@
       <c r="D7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="111" t="s">
+      <c r="E7" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="113"/>
+      <c r="F7" s="106"/>
       <c r="G7" s="11" t="s">
         <v>34</v>
       </c>
@@ -2082,10 +2086,10 @@
       <c r="R7" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="S7" s="109"/>
-      <c r="T7" s="107"/>
-      <c r="U7" s="115"/>
-      <c r="V7" s="117"/>
+      <c r="S7" s="116"/>
+      <c r="T7" s="114"/>
+      <c r="U7" s="120"/>
+      <c r="V7" s="122"/>
     </row>
     <row r="8" spans="1:24" s="28" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="67"/>
@@ -2124,10 +2128,10 @@
       <c r="R9" s="72"/>
       <c r="S9" s="72"/>
       <c r="T9" s="72"/>
-      <c r="U9" s="118" t="s">
+      <c r="U9" s="123" t="s">
         <v>84</v>
       </c>
-      <c r="V9" s="119"/>
+      <c r="V9" s="124"/>
       <c r="X9"/>
     </row>
     <row r="10" spans="1:24" s="28" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -2143,10 +2147,10 @@
       <c r="D10" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="120" t="s">
+      <c r="E10" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="121"/>
+      <c r="F10" s="108"/>
       <c r="G10" s="65" t="s">
         <v>5</v>
       </c>
@@ -2342,23 +2346,23 @@
       <c r="A16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
-      <c r="E16" s="123" t="s">
+      <c r="E16" s="110" t="s">
         <v>48</v>
       </c>
       <c r="G16" s="24"/>
       <c r="H16" s="15"/>
       <c r="I16" s="14"/>
-      <c r="J16" s="105" t="s">
+      <c r="J16" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="K16" s="105"/>
+      <c r="K16" s="111"/>
       <c r="L16" s="14"/>
       <c r="N16" s="16"/>
       <c r="P16" s="14"/>
-      <c r="Q16" s="110" t="s">
+      <c r="Q16" s="117" t="s">
         <v>50</v>
       </c>
-      <c r="R16" s="110"/>
+      <c r="R16" s="117"/>
       <c r="S16" s="47"/>
       <c r="T16" s="14"/>
       <c r="U16" s="12"/>
@@ -2377,15 +2381,15 @@
         <v>94</v>
       </c>
       <c r="D17" s="17"/>
-      <c r="E17" s="123"/>
+      <c r="E17" s="110"/>
       <c r="F17" s="41" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="17"/>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
-      <c r="J17" s="105"/>
-      <c r="K17" s="105"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="111"/>
       <c r="L17" s="41" t="s">
         <v>88</v>
       </c>
@@ -2393,8 +2397,8 @@
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
       <c r="P17" s="19"/>
-      <c r="Q17" s="110"/>
-      <c r="R17" s="110"/>
+      <c r="Q17" s="117"/>
+      <c r="R17" s="117"/>
       <c r="S17" s="41" t="s">
         <v>89</v>
       </c>
@@ -2430,17 +2434,17 @@
       <c r="E19" s="30"/>
       <c r="F19" s="14"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="105" t="s">
+      <c r="J19" s="111" t="s">
         <v>53</v>
       </c>
-      <c r="K19" s="105"/>
+      <c r="K19" s="111"/>
       <c r="M19"/>
       <c r="N19" s="1"/>
       <c r="O19" s="12"/>
-      <c r="Q19" s="105" t="s">
+      <c r="Q19" s="111" t="s">
         <v>95</v>
       </c>
-      <c r="R19" s="105"/>
+      <c r="R19" s="111"/>
       <c r="S19" s="1"/>
       <c r="T19"/>
       <c r="V19" s="12"/>
@@ -2454,55 +2458,50 @@
       <c r="C20" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="17"/>
+      <c r="D20" s="103"/>
       <c r="E20" s="35" t="s">
         <v>52</v>
       </c>
       <c r="F20" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="105"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="103"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="111"/>
       <c r="L20" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="M20" s="19"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="105"/>
-      <c r="R20" s="105"/>
+      <c r="M20" s="104"/>
+      <c r="N20" s="103"/>
+      <c r="O20" s="103"/>
+      <c r="P20" s="103"/>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="111"/>
       <c r="S20" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="T20" s="19"/>
-      <c r="U20" s="17"/>
-      <c r="V20" s="17"/>
+      <c r="T20" s="104"/>
+      <c r="U20" s="103"/>
+      <c r="V20" s="103"/>
       <c r="X20"/>
     </row>
     <row r="21" spans="1:24" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="33"/>
-      <c r="D21" s="37"/>
       <c r="E21" s="18"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="37"/>
+      <c r="F21" s="34"/>
       <c r="I21" s="21"/>
       <c r="K21" s="18"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
       <c r="Q21" s="21"/>
       <c r="V21" s="102"/>
     </row>
     <row r="22" spans="1:24" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
-      <c r="B22" s="31"/>
+      <c r="A22" s="110" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="110"/>
       <c r="D22" s="1"/>
       <c r="E22" s="30"/>
       <c r="F22" s="14"/>
@@ -2512,43 +2511,46 @@
       <c r="M22"/>
       <c r="N22" s="1"/>
       <c r="O22" s="12"/>
+      <c r="Q22" s="110" t="s">
+        <v>97</v>
+      </c>
+      <c r="R22" s="110"/>
+      <c r="S22" s="1"/>
       <c r="T22"/>
-      <c r="U22"/>
-      <c r="V22" s="103"/>
+      <c r="V22" s="12"/>
       <c r="W22"/>
       <c r="X22"/>
     </row>
     <row r="23" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-      <c r="B23" s="35" t="s">
-        <v>71</v>
-      </c>
+      <c r="A23" s="110"/>
+      <c r="B23" s="110"/>
       <c r="C23" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="17"/>
+      <c r="D23" s="103"/>
       <c r="E23" s="35" t="s">
         <v>54</v>
       </c>
       <c r="F23" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="124"/>
-      <c r="P23" s="124"/>
-      <c r="Q23" s="124"/>
-      <c r="R23" s="124"/>
-      <c r="S23" s="125"/>
-      <c r="T23" s="125"/>
-      <c r="U23" s="125"/>
-      <c r="V23" s="126"/>
+        <v>98</v>
+      </c>
+      <c r="G23" s="103"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="103"/>
+      <c r="J23" s="103"/>
+      <c r="K23" s="103"/>
+      <c r="L23" s="103"/>
+      <c r="M23" s="103"/>
+      <c r="N23" s="103"/>
+      <c r="O23" s="103"/>
+      <c r="Q23" s="110"/>
+      <c r="R23" s="110"/>
+      <c r="S23" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="T23" s="104"/>
+      <c r="U23" s="103"/>
+      <c r="V23" s="103"/>
       <c r="W23"/>
       <c r="X23"/>
     </row>
@@ -2887,12 +2889,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="16">
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="K3:O3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="J16:K17"/>
+  <mergeCells count="18">
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="Q22:R23"/>
     <mergeCell ref="K1:V1"/>
     <mergeCell ref="J19:K20"/>
     <mergeCell ref="T6:T7"/>
@@ -2904,6 +2903,11 @@
     <mergeCell ref="V6:V7"/>
     <mergeCell ref="U9:V9"/>
     <mergeCell ref="Q19:R20"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="K3:O3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="J16:K17"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:D8">
     <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">
@@ -2921,7 +2925,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="G16 H11:H13" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>

--- a/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -446,12 +446,29 @@
   </si>
   <si>
     <t>${session.reserveJuryAsTO} ${session.reserveJuryAsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.marshallAsTO} ${session.marshallAsTO.federation}
+${session.marshal2AsTO} ${session.marshal2AsTO.federation}</t>
+  </si>
+  <si>
+    <t>${session.technicalControllerAsTO} ${session.technicalControllerAsTO.federation}
+${session.technicalController2AsTO} ${session.technicalController2AsTO.federation}</t>
+  </si>
+  <si>
+    <t>${t.get("Doctor")}</t>
+  </si>
+  <si>
+    <t>${session.timeKeeperAsTO} ${session.timeKeeperAsTO.federation}</t>
+  </si>
+  <si>
+    <t>${session.doctorAsTO} ${session.doctorAsTO.federation}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0;;"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_)\ _$_ ;_ * \(#,##0&quot;) &quot;_$_ ;_ * \-??_)\ _$_ ;_ @_ "/>
@@ -460,7 +477,7 @@
     <numFmt numFmtId="168" formatCode="0.000;;\-"/>
     <numFmt numFmtId="169" formatCode="0;\-;\-"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="46" ns2:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -650,8 +667,91 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -729,8 +829,53 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1012,6 +1157,121 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color indexed="8"/>
       </bottom>
@@ -1039,7 +1299,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1388,6 +1648,47 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="24" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="25" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="26" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="27" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="28" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="30" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="31" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="39" fillId="22" borderId="32" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="33" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="24" borderId="34" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="25" borderId="35" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="26" borderId="36" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="37" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="28" borderId="38" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -1397,18 +1698,18 @@
     <cellStyle name="Accent4" xfId="4" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="5" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="6" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Emphase 1" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Emphase 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Emphase 3" xfId="9" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Emphase 1" xfId="7" ns3:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Emphase 2" xfId="8" ns3:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Emphase 3" xfId="9" ns3:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Hyperlink" xfId="10" builtinId="8"/>
-    <cellStyle name="Lien hypertexte 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Lien hypertexte 2" xfId="11" ns3:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Normal 3" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Titre 1" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Titre 1 1" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Titre 1 1 1" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Titre de la feuille" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Normal 2" xfId="12" ns3:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 3" xfId="13" ns3:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Titre 1" xfId="14" ns3:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Titre 1 1" xfId="15" ns3:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Titre 1 1 1" xfId="16" ns3:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Titre de la feuille" xfId="17" ns3:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="3">
@@ -1507,11 +1808,11 @@
     </indexedColors>
   </colors>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns4:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns5:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1864,12 +2165,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Feuil4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X125"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" style="1" customWidth="1"/>
@@ -1893,7 +2194,7 @@
     <col min="25" max="25" width="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="49" t="s">
         <v>20</v>
       </c>
@@ -1921,7 +2222,7 @@
       <c r="U1" s="112"/>
       <c r="V1" s="112"/>
     </row>
-    <row r="2" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A2" s="52" t="s">
         <v>21</v>
       </c>
@@ -1947,7 +2248,7 @@
       </c>
       <c r="T2" s="57"/>
     </row>
-    <row r="3" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>22</v>
       </c>
@@ -1974,7 +2275,7 @@
       <c r="U3" s="96"/>
       <c r="V3" s="96"/>
     </row>
-    <row r="4" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A4" s="58" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2297,8 @@
       <c r="R4" s="32"/>
       <c r="S4" s="63"/>
     </row>
-    <row r="5" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" ht="6" customHeight="1" ns3:dyDescent="0.2"/>
+    <row r="6" spans="1:24" ht="15" customHeight="1" ns3:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="C6" s="8"/>
       <c r="H6" s="7"/>
@@ -2033,7 +2334,7 @@
       </c>
       <c r="X6"/>
     </row>
-    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>40</v>
       </c>
@@ -2091,7 +2392,7 @@
       <c r="U7" s="120"/>
       <c r="V7" s="122"/>
     </row>
-    <row r="8" spans="1:24" s="28" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" s="28" customFormat="1" ht="7.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A8" s="67"/>
       <c r="B8" s="67"/>
       <c r="C8" s="67"/>
@@ -2105,7 +2406,7 @@
       <c r="K8" s="69"/>
       <c r="V8" s="98"/>
     </row>
-    <row r="9" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="21.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A9" s="70" t="s">
         <v>56</v>
       </c>
@@ -2134,7 +2435,7 @@
       <c r="V9" s="124"/>
       <c r="X9"/>
     </row>
-    <row r="10" spans="1:24" s="28" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" s="28" customFormat="1" ht="21.2" customHeight="1" ns3:dyDescent="0.2">
       <c r="A10" s="25" t="s">
         <v>2</v>
       </c>
@@ -2200,7 +2501,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="24.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="B11"/>
       <c r="G11"/>
       <c r="H11"/>
@@ -2218,13 +2519,13 @@
       <c r="W11"/>
       <c r="X11"/>
     </row>
-    <row r="12" spans="1:24" s="49" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="49" customFormat="1" ht="15" ns3:dyDescent="0.25">
       <c r="A12" s="49" t="s">
         <v>65</v>
       </c>
       <c r="J12" s="50"/>
     </row>
-    <row r="13" spans="1:24" s="49" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="49" customFormat="1" ht="6.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A13" s="74"/>
       <c r="B13" s="74"/>
       <c r="C13" s="74"/>
@@ -2248,7 +2549,7 @@
       <c r="U13" s="80"/>
       <c r="V13" s="80"/>
     </row>
-    <row r="14" spans="1:24" s="92" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" s="92" customFormat="1" ht="12" ns3:dyDescent="0.2">
       <c r="A14" s="83" t="s">
         <v>73</v>
       </c>
@@ -2295,7 +2596,7 @@
       <c r="V14" s="91"/>
       <c r="X14" s="85"/>
     </row>
-    <row r="15" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" s="73" customFormat="1" ns3:dyDescent="0.2">
       <c r="A15" s="75" t="s">
         <v>58</v>
       </c>
@@ -2342,92 +2643,80 @@
       <c r="V15" s="77"/>
       <c r="X15" s="77"/>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="110" t="s">
+    <row r="16" spans="1:24" ht="6" customHeight="1" ns3:dyDescent="0.2">
+      <c r="C16" s="125"/>
+      <c r="D16" s="125"/>
+    </row>
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" ns3:dyDescent="0.2">
+      <c r="A17" s="126" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="24"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="111" t="s">
+      <c r="B17" s="126"/>
+      <c r="C17" s="127" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="127"/>
+      <c r="E17" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="K16" s="111"/>
-      <c r="L16" s="14"/>
-      <c r="N16" s="16"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="117" t="s">
+      <c r="F17" s="128"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="131"/>
+      <c r="J17" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="R16" s="117"/>
-      <c r="S16" s="47"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="14"/>
-      <c r="X16" s="14" t="s">
+      <c r="K17" s="126"/>
+      <c r="L17" s="127" t="s">
+        <v>101</v>
+      </c>
+      <c r="M17" s="127"/>
+      <c r="N17" s="127"/>
+      <c r="O17" s="127"/>
+      <c r="P17" s="127"/>
+      <c r="Q17" s="132" t="s">
+        <v>102</v>
+      </c>
+      <c r="R17" s="132"/>
+      <c r="S17" s="129"/>
+      <c r="T17" s="130"/>
+      <c r="U17" s="131"/>
+      <c r="V17" s="133"/>
+      <c r="W17" s="134"/>
+      <c r="X17" s="134" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="111"/>
-      <c r="L17" s="41" t="s">
-        <v>88</v>
-      </c>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="117"/>
-      <c r="S17" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="T17" s="19"/>
-      <c r="U17" s="17"/>
-      <c r="V17" s="101"/>
-      <c r="W17"/>
-    </row>
-    <row r="18" spans="1:24" s="20" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
-      <c r="B18" s="33"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="37"/>
-      <c r="I18" s="21"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="21"/>
-      <c r="S18" s="37"/>
-      <c r="T18" s="37"/>
-      <c r="U18" s="37"/>
-      <c r="V18" s="102"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" ht="16.5" customHeight="1" ns3:dyDescent="0.2">
+      <c r="A18" s="126"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="135"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="136" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" s="137"/>
+      <c r="H18" s="138"/>
+      <c r="I18" s="139"/>
+      <c r="J18" s="126"/>
+      <c r="K18" s="126"/>
+      <c r="L18" s="135"/>
+      <c r="M18" s="135"/>
+      <c r="N18" s="135"/>
+      <c r="O18" s="135"/>
+      <c r="P18" s="135"/>
+      <c r="Q18" s="132"/>
+      <c r="R18" s="132"/>
+      <c r="S18" s="136" t="s">
+        <v>104</v>
+      </c>
+      <c r="T18" s="138"/>
+      <c r="U18" s="139"/>
+      <c r="V18" s="139"/>
+      <c r="W18"/>
+    </row>
+    <row r="19" spans="1:24" ns3:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="31"/>
       <c r="D19" s="1"/>
@@ -2450,7 +2739,7 @@
       <c r="V19" s="12"/>
       <c r="X19"/>
     </row>
-    <row r="20" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="13.7" customHeight="1" ns3:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="35" t="s">
         <v>51</v>
@@ -2487,7 +2776,7 @@
       <c r="V20" s="103"/>
       <c r="X20"/>
     </row>
-    <row r="21" spans="1:24" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" s="20" customFormat="1" ht="12.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="33"/>
       <c r="E21" s="18"/>
@@ -2497,7 +2786,7 @@
       <c r="Q21" s="21"/>
       <c r="V21" s="102"/>
     </row>
-    <row r="22" spans="1:24" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" ht="17.45" customHeight="1" ns3:dyDescent="0.2">
       <c r="A22" s="110" t="s">
         <v>71</v>
       </c>
@@ -2521,7 +2810,7 @@
       <c r="W22"/>
       <c r="X22"/>
     </row>
-    <row r="23" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" ht="13.7" customHeight="1" ns3:dyDescent="0.2">
       <c r="A23" s="110"/>
       <c r="B23" s="110"/>
       <c r="C23" s="41" t="s">
@@ -2554,7 +2843,7 @@
       <c r="W23"/>
       <c r="X23"/>
     </row>
-    <row r="24" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" s="20" customFormat="1" ns3:dyDescent="0.2">
       <c r="B24" s="21"/>
       <c r="D24" s="37"/>
       <c r="F24" s="15"/>
@@ -2573,7 +2862,7 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" ns3:dyDescent="0.2">
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="H25" s="2"/>
@@ -2585,318 +2874,317 @@
       <c r="S25" s="1"/>
       <c r="T25" s="12"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" ns3:dyDescent="0.2">
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" ns3:dyDescent="0.2">
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24" ns3:dyDescent="0.2">
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" ns3:dyDescent="0.2">
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" ns3:dyDescent="0.2">
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" ns3:dyDescent="0.2">
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" ns3:dyDescent="0.2">
       <c r="F32" s="1"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="6:6" ns3:dyDescent="0.2">
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="6:6" ns3:dyDescent="0.2">
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="6:6" ns3:dyDescent="0.2">
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="6:6" ns3:dyDescent="0.2">
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="6:6" ns3:dyDescent="0.2">
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="6:6" ns3:dyDescent="0.2">
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="6:6" ns3:dyDescent="0.2">
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="6:6" ns3:dyDescent="0.2">
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="6:6" ns3:dyDescent="0.2">
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="6:6" ns3:dyDescent="0.2">
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="6:6" ns3:dyDescent="0.2">
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="6:6" ns3:dyDescent="0.2">
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="6:6" ns3:dyDescent="0.2">
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="6:6" ns3:dyDescent="0.2">
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="6:6" ns3:dyDescent="0.2">
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="6:6" ns3:dyDescent="0.2">
       <c r="F48" s="1"/>
     </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="6:6" ns3:dyDescent="0.2">
       <c r="F49" s="1"/>
     </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="6:6" ns3:dyDescent="0.2">
       <c r="F50" s="1"/>
     </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="6:6" ns3:dyDescent="0.2">
       <c r="F51" s="1"/>
     </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="6:6" ns3:dyDescent="0.2">
       <c r="F52" s="1"/>
     </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="6:6" ns3:dyDescent="0.2">
       <c r="F53" s="1"/>
     </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="6:6" ns3:dyDescent="0.2">
       <c r="F54" s="1"/>
     </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="6:6" ns3:dyDescent="0.2">
       <c r="F55" s="1"/>
     </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="6:6" ns3:dyDescent="0.2">
       <c r="F56" s="1"/>
     </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="6:6" ns3:dyDescent="0.2">
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="6:6" ns3:dyDescent="0.2">
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="6:6" ns3:dyDescent="0.2">
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="6:6" ns3:dyDescent="0.2">
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="6:6" ns3:dyDescent="0.2">
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="6:6" ns3:dyDescent="0.2">
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="6:6" ns3:dyDescent="0.2">
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="6:6" ns3:dyDescent="0.2">
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="6:6" ns3:dyDescent="0.2">
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="6:6" ns3:dyDescent="0.2">
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="6:6" ns3:dyDescent="0.2">
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="6:6" ns3:dyDescent="0.2">
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="6:6" ns3:dyDescent="0.2">
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="6:6" ns3:dyDescent="0.2">
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="6:6" ns3:dyDescent="0.2">
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="6:6" ns3:dyDescent="0.2">
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="6:6" ns3:dyDescent="0.2">
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="6:6" ns3:dyDescent="0.2">
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="6:6" ns3:dyDescent="0.2">
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="6:6" ns3:dyDescent="0.2">
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="6:6" ns3:dyDescent="0.2">
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="6:6" ns3:dyDescent="0.2">
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="6:6" ns3:dyDescent="0.2">
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="6:6" ns3:dyDescent="0.2">
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="6:6" ns3:dyDescent="0.2">
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="6:6" ns3:dyDescent="0.2">
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="6:6" ns3:dyDescent="0.2">
       <c r="F83" s="1"/>
     </row>
-    <row r="84" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="6:6" ns3:dyDescent="0.2">
       <c r="F84" s="1"/>
     </row>
-    <row r="85" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="6:6" ns3:dyDescent="0.2">
       <c r="F85" s="1"/>
     </row>
-    <row r="86" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="6:6" ns3:dyDescent="0.2">
       <c r="F86" s="1"/>
     </row>
-    <row r="87" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="6:6" ns3:dyDescent="0.2">
       <c r="F87" s="1"/>
     </row>
-    <row r="88" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="6:6" ns3:dyDescent="0.2">
       <c r="F88" s="1"/>
     </row>
-    <row r="89" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="6:6" ns3:dyDescent="0.2">
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="6:6" ns3:dyDescent="0.2">
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="6:6" ns3:dyDescent="0.2">
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="6:6" ns3:dyDescent="0.2">
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="6:6" ns3:dyDescent="0.2">
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="6:6" ns3:dyDescent="0.2">
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="6:6" ns3:dyDescent="0.2">
       <c r="F95" s="1"/>
     </row>
-    <row r="96" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="6:6" ns3:dyDescent="0.2">
       <c r="F96" s="1"/>
     </row>
-    <row r="97" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="6:6" ns3:dyDescent="0.2">
       <c r="F97" s="1"/>
     </row>
-    <row r="98" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="6:6" ns3:dyDescent="0.2">
       <c r="F98" s="1"/>
     </row>
-    <row r="99" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="6:6" ns3:dyDescent="0.2">
       <c r="F99" s="1"/>
     </row>
-    <row r="100" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="6:6" ns3:dyDescent="0.2">
       <c r="F100" s="1"/>
     </row>
-    <row r="101" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="6:6" ns3:dyDescent="0.2">
       <c r="F101" s="1"/>
     </row>
-    <row r="102" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="6:6" ns3:dyDescent="0.2">
       <c r="F102" s="1"/>
     </row>
-    <row r="103" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="6:6" ns3:dyDescent="0.2">
       <c r="F103" s="1"/>
     </row>
-    <row r="104" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="6:6" ns3:dyDescent="0.2">
       <c r="F104" s="1"/>
     </row>
-    <row r="105" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="6:6" ns3:dyDescent="0.2">
       <c r="F105" s="1"/>
     </row>
-    <row r="106" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="6:6" ns3:dyDescent="0.2">
       <c r="F106" s="1"/>
     </row>
-    <row r="107" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="6:6" ns3:dyDescent="0.2">
       <c r="F107" s="1"/>
     </row>
-    <row r="108" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="6:6" ns3:dyDescent="0.2">
       <c r="F108" s="1"/>
     </row>
-    <row r="109" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="6:6" ns3:dyDescent="0.2">
       <c r="F109" s="1"/>
     </row>
-    <row r="110" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="6:6" ns3:dyDescent="0.2">
       <c r="F110" s="1"/>
     </row>
-    <row r="111" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="6:6" ns3:dyDescent="0.2">
       <c r="F111" s="1"/>
     </row>
-    <row r="112" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="6:6" ns3:dyDescent="0.2">
       <c r="F112" s="1"/>
     </row>
-    <row r="113" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="6:6" ns3:dyDescent="0.2">
       <c r="F113" s="1"/>
     </row>
-    <row r="114" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="6:6" ns3:dyDescent="0.2">
       <c r="F114" s="1"/>
     </row>
-    <row r="115" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="6:6" ns3:dyDescent="0.2">
       <c r="F115" s="1"/>
     </row>
-    <row r="116" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="6:6" ns3:dyDescent="0.2">
       <c r="F116" s="1"/>
     </row>
-    <row r="117" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="6:6" ns3:dyDescent="0.2">
       <c r="F117" s="1"/>
     </row>
-    <row r="118" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="6:6" ns3:dyDescent="0.2">
       <c r="F118" s="1"/>
     </row>
-    <row r="119" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="6:6" ns3:dyDescent="0.2">
       <c r="F119" s="1"/>
     </row>
-    <row r="120" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="6:6" ns3:dyDescent="0.2">
       <c r="F120" s="1"/>
     </row>
-    <row r="121" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="6:6" ns3:dyDescent="0.2">
       <c r="F121" s="1"/>
     </row>
-    <row r="122" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="6:6" ns3:dyDescent="0.2">
       <c r="F122" s="1"/>
     </row>
-    <row r="123" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="6:6" ns3:dyDescent="0.2">
       <c r="F123" s="1"/>
     </row>
-    <row r="124" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="6:6" ns3:dyDescent="0.2">
       <c r="F124" s="1"/>
     </row>
-    <row r="125" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="6:6" ns3:dyDescent="0.2">
       <c r="F125" s="1"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="18">
+  <mergeCells count="21">
     <mergeCell ref="A22:B23"/>
     <mergeCell ref="Q22:R23"/>
     <mergeCell ref="K1:V1"/>
     <mergeCell ref="J19:K20"/>
     <mergeCell ref="T6:T7"/>
     <mergeCell ref="S6:S7"/>
-    <mergeCell ref="Q16:R17"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="O6:Q6"/>
     <mergeCell ref="U6:U7"/>
@@ -2906,8 +3194,12 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="K3:O3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="J16:K17"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="L17:P18"/>
+    <mergeCell ref="J17:K18"/>
+    <mergeCell ref="Q17:R18"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:D8">
     <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">
@@ -2925,24 +3217,24 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="G16 H11:H13" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" ns2:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" ns2:uid="{00000000-0002-0000-0000-000001000000}"/>
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="G16 H11:H13" ns2:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" ns2:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" display="www.federation.org" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A4" r:id="rId2" display="records@federation.org" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A3" ns4:id="rId1" display="www.federation.org" ns2:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A4" ns4:id="rId2" display="records@federation.org" ns2:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="71" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
+  <pageSetup paperSize="9" scale="71" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns4:id="rId3"/>
   <headerFooter alignWithMargins="0"/>
-  <legacyDrawing r:id="rId4"/>
+  <legacyDrawing ns4:id="rId4"/>
 </worksheet>
 </file>
--- a/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
@@ -468,7 +468,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0;;"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_)\ _$_ ;_ * \(#,##0&quot;) &quot;_$_ ;_ * \-??_)\ _$_ ;_ @_ "/>
@@ -2165,7 +2165,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Feuil4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
@@ -124,7 +124,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:if(condition="records != null" lastCell="V15")</t>
+          <t>jx:if(condition="session.records.size() &gt; 0" lastCell="V15")</t>
         </r>
       </text>
     </comment>
@@ -137,7 +137,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:each(items="records" var="r" lastCell="V15")</t>
+          <t>jx:each(items="session.records" var="r" lastCell="V15")</t>
         </r>
       </text>
     </comment>
@@ -468,7 +468,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0;;"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_)\ _$_ ;_ * \(#,##0&quot;) &quot;_$_ ;_ * \-??_)\ _$_ ;_ @_ "/>
@@ -477,7 +477,7 @@
     <numFmt numFmtId="168" formatCode="0.000;;\-"/>
     <numFmt numFmtId="169" formatCode="0;\-;\-"/>
   </numFmts>
-  <fonts count="46" ns2:knownFonts="1">
+  <fonts count="135" ns1:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -749,6 +749,559 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="29">
@@ -875,7 +1428,7 @@
       <patternFill patternType="none"/>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="126">
     <border>
       <left/>
       <right/>
@@ -1276,6 +1829,639 @@
         <color indexed="8"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="19">
@@ -1299,7 +2485,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1689,6 +2875,313 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="28" borderId="38" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="39" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="40" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="41" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="42" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="43" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="44" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="45" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="46" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="47" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="48" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="49" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="50" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="54" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="55" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="56" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="57" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="58" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="59" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="60" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="61" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="62" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="70" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="71" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="72" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="76" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="77" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="78" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="75" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="76" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="77" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="78" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="79" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="80" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="81" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="82" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="83" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="84" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="85" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="86" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="87" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="88" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="89" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="90" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="93" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="94" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="95" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="96" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="97" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="98" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="99" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="100" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="101" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="104" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="105" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="107" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="108" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="109" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="110" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="111" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="112" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="113" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="114" xfId="0" applyFont="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="115" xfId="0" applyFont="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="116" xfId="0" applyFont="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="124" fillId="0" borderId="117" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="125" fillId="0" borderId="118" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="126" fillId="0" borderId="119" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="120" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="121" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="122" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="123" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="124" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="125" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="0" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1" applyAlignment="1" applyBorder="0">
+      <protection locked="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0" applyFont="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0" applyFont="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -1698,18 +3191,18 @@
     <cellStyle name="Accent4" xfId="4" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="5" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="6" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Emphase 1" xfId="7" ns3:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Emphase 2" xfId="8" ns3:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Emphase 3" xfId="9" ns3:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Emphase 1" xfId="7" ns2:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Emphase 2" xfId="8" ns2:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Emphase 3" xfId="9" ns2:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Hyperlink" xfId="10" builtinId="8"/>
-    <cellStyle name="Lien hypertexte 2" xfId="11" ns3:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Lien hypertexte 2" xfId="11" ns2:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="12" ns3:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Normal 3" xfId="13" ns3:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Titre 1" xfId="14" ns3:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Titre 1 1" xfId="15" ns3:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Titre 1 1 1" xfId="16" ns3:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Titre de la feuille" xfId="17" ns3:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Normal 2" xfId="12" ns2:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 3" xfId="13" ns2:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Titre 1" xfId="14" ns2:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Titre 1 1" xfId="15" ns2:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Titre 1 1 1" xfId="16" ns2:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Titre de la feuille" xfId="17" ns2:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="3">
@@ -1809,10 +3302,10 @@
   </colors>
   <extLst>
     <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <ns4:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
     <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <ns5:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2165,12 +3658,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Feuil4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X125"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" ns3:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" ns2:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" style="1" customWidth="1"/>
@@ -2194,111 +3687,71 @@
     <col min="25" max="25" width="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="15"/>
-      <c r="J1" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="112" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-    </row>
-    <row r="2" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="4"/>
-      <c r="J2" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="54" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="95"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T2" s="57"/>
-    </row>
-    <row r="3" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="59"/>
-      <c r="J3" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="109" t="s">
-        <v>57</v>
-      </c>
-      <c r="L3" s="109"/>
-      <c r="M3" s="109"/>
-      <c r="N3" s="109"/>
-      <c r="O3" s="109"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="T3" s="62"/>
-      <c r="U3" s="96"/>
-      <c r="V3" s="96"/>
-    </row>
-    <row r="4" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
-      <c r="A4" s="58" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="J4" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="K4" s="97" t="s">
-        <v>81</v>
-      </c>
-      <c r="L4"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="Q4"/>
-      <c r="R4" s="32"/>
-      <c r="S4" s="63"/>
-    </row>
-    <row r="5" spans="1:24" ht="6" customHeight="1" ns3:dyDescent="0.2"/>
-    <row r="6" spans="1:24" ht="15" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="24" customHeight="1" ns2:dyDescent="0.25">
+      <c r="A1" s="228" t="inlineStr">
+        <is>
+          <t>${competition.competitionName}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="24" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A2" s="227" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionSite")} :</t>
+        </is>
+      </c>
+      <c r="D2" s="229" t="inlineStr">
+        <is>
+          <t>${competition.competitionSite}</t>
+        </is>
+      </c>
+      <c r="K2" s="227" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionCity")} :</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr" s="230">
+        <is>
+          <t>${competition.competitionCity}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="24" customHeight="1" ns2:dyDescent="0.25">
+      <c r="A3" s="227" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionDate")} :</t>
+        </is>
+      </c>
+      <c r="D3" s="231" t="inlineStr">
+        <is>
+          <t>${competition.localizedCompetitionDate}</t>
+        </is>
+      </c>
+      <c r="K3" s="234" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionOrganizer")} :</t>
+        </is>
+      </c>
+      <c r="N3" s="232" t="inlineStr">
+        <is>
+          <t>${competition.competitionOrganizer}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="24" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A4" s="235" t="inlineStr">
+        <is>
+          <t>${session != null ? t.get("Group") + " :" : ""}</t>
+        </is>
+      </c>
+      <c r="D4" s="233" t="inlineStr">
+        <is>
+          <t>${session != null ? session.name : ""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="6" customHeight="1" ns2:dyDescent="0.2"/>
+    <row r="6" spans="1:24" ht="15" customHeight="1" ns2:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="C6" s="8"/>
       <c r="H6" s="7"/>
@@ -2334,7 +3787,7 @@
       </c>
       <c r="X6"/>
     </row>
-    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.2">
+    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" ns2:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>40</v>
       </c>
@@ -2392,7 +3845,7 @@
       <c r="U7" s="120"/>
       <c r="V7" s="122"/>
     </row>
-    <row r="8" spans="1:24" s="28" customFormat="1" ht="7.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="8" spans="1:24" s="28" customFormat="1" ht="7.5" customHeight="1" ns2:dyDescent="0.2">
       <c r="A8" s="67"/>
       <c r="B8" s="67"/>
       <c r="C8" s="67"/>
@@ -2406,7 +3859,7 @@
       <c r="K8" s="69"/>
       <c r="V8" s="98"/>
     </row>
-    <row r="9" spans="1:24" ht="21.75" customHeight="1" ns3:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="21.75" customHeight="1" ns2:dyDescent="0.2">
       <c r="A9" s="70" t="s">
         <v>56</v>
       </c>
@@ -2435,7 +3888,7 @@
       <c r="V9" s="124"/>
       <c r="X9"/>
     </row>
-    <row r="10" spans="1:24" s="28" customFormat="1" ht="21.2" customHeight="1" ns3:dyDescent="0.2">
+    <row r="10" spans="1:24" s="28" customFormat="1" ht="21.2" customHeight="1" ns2:dyDescent="0.2">
       <c r="A10" s="25" t="s">
         <v>2</v>
       </c>
@@ -2501,7 +3954,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="24.75" customHeight="1" ns3:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="24.75" customHeight="1" ns2:dyDescent="0.2">
       <c r="B11"/>
       <c r="G11"/>
       <c r="H11"/>
@@ -2519,13 +3972,13 @@
       <c r="W11"/>
       <c r="X11"/>
     </row>
-    <row r="12" spans="1:24" s="49" customFormat="1" ht="15" ns3:dyDescent="0.25">
+    <row r="12" spans="1:24" s="49" customFormat="1" ht="15" ns2:dyDescent="0.25">
       <c r="A12" s="49" t="s">
         <v>65</v>
       </c>
       <c r="J12" s="50"/>
     </row>
-    <row r="13" spans="1:24" s="49" customFormat="1" ht="6.75" customHeight="1" ns3:dyDescent="0.25">
+    <row r="13" spans="1:24" s="49" customFormat="1" ht="6.75" customHeight="1" ns2:dyDescent="0.25">
       <c r="A13" s="74"/>
       <c r="B13" s="74"/>
       <c r="C13" s="74"/>
@@ -2549,7 +4002,7 @@
       <c r="U13" s="80"/>
       <c r="V13" s="80"/>
     </row>
-    <row r="14" spans="1:24" s="92" customFormat="1" ht="12" ns3:dyDescent="0.2">
+    <row r="14" spans="1:24" s="92" customFormat="1" ht="12" ns2:dyDescent="0.2">
       <c r="A14" s="83" t="s">
         <v>73</v>
       </c>
@@ -2596,7 +4049,7 @@
       <c r="V14" s="91"/>
       <c r="X14" s="85"/>
     </row>
-    <row r="15" spans="1:24" s="73" customFormat="1" ns3:dyDescent="0.2">
+    <row r="15" spans="1:24" s="73" customFormat="1" ns2:dyDescent="0.2">
       <c r="A15" s="75" t="s">
         <v>58</v>
       </c>
@@ -2643,11 +4096,11 @@
       <c r="V15" s="77"/>
       <c r="X15" s="77"/>
     </row>
-    <row r="16" spans="1:24" ht="6" customHeight="1" ns3:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="6" customHeight="1" ns2:dyDescent="0.2">
       <c r="C16" s="125"/>
       <c r="D16" s="125"/>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" ns3:dyDescent="0.2">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" ns2:dyDescent="0.2">
       <c r="A17" s="126" t="s">
         <v>48</v>
       </c>
@@ -2687,7 +4140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="16.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="18" spans="1:24" ht="16.5" customHeight="1" ns2:dyDescent="0.2">
       <c r="A18" s="126"/>
       <c r="B18" s="126"/>
       <c r="C18" s="135"/>
@@ -2716,7 +4169,7 @@
       <c r="V18" s="139"/>
       <c r="W18"/>
     </row>
-    <row r="19" spans="1:24" ns3:dyDescent="0.2">
+    <row r="19" spans="1:24" ns2:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="31"/>
       <c r="D19" s="1"/>
@@ -2739,7 +4192,7 @@
       <c r="V19" s="12"/>
       <c r="X19"/>
     </row>
-    <row r="20" spans="1:24" ht="13.7" customHeight="1" ns3:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="13.7" customHeight="1" ns2:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="35" t="s">
         <v>51</v>
@@ -2776,7 +4229,7 @@
       <c r="V20" s="103"/>
       <c r="X20"/>
     </row>
-    <row r="21" spans="1:24" s="20" customFormat="1" ht="12.75" customHeight="1" ns3:dyDescent="0.2">
+    <row r="21" spans="1:24" s="20" customFormat="1" ht="12.75" customHeight="1" ns2:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="33"/>
       <c r="E21" s="18"/>
@@ -2786,7 +4239,7 @@
       <c r="Q21" s="21"/>
       <c r="V21" s="102"/>
     </row>
-    <row r="22" spans="1:24" ht="17.45" customHeight="1" ns3:dyDescent="0.2">
+    <row r="22" spans="1:24" ht="17.45" customHeight="1" ns2:dyDescent="0.2">
       <c r="A22" s="110" t="s">
         <v>71</v>
       </c>
@@ -2810,7 +4263,7 @@
       <c r="W22"/>
       <c r="X22"/>
     </row>
-    <row r="23" spans="1:24" ht="13.7" customHeight="1" ns3:dyDescent="0.2">
+    <row r="23" spans="1:24" ht="13.7" customHeight="1" ns2:dyDescent="0.2">
       <c r="A23" s="110"/>
       <c r="B23" s="110"/>
       <c r="C23" s="41" t="s">
@@ -2843,7 +4296,7 @@
       <c r="W23"/>
       <c r="X23"/>
     </row>
-    <row r="24" spans="1:24" s="20" customFormat="1" ns3:dyDescent="0.2">
+    <row r="24" spans="1:24" s="20" customFormat="1" ns2:dyDescent="0.2">
       <c r="B24" s="21"/>
       <c r="D24" s="37"/>
       <c r="F24" s="15"/>
@@ -2862,7 +4315,7 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="1:24" ns3:dyDescent="0.2">
+    <row r="25" spans="1:24" ns2:dyDescent="0.2">
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="H25" s="2"/>
@@ -2874,314 +4327,313 @@
       <c r="S25" s="1"/>
       <c r="T25" s="12"/>
     </row>
-    <row r="26" spans="1:24" ns3:dyDescent="0.2">
+    <row r="26" spans="1:24" ns2:dyDescent="0.2">
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:24" ns3:dyDescent="0.2">
+    <row r="27" spans="1:24" ns2:dyDescent="0.2">
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:24" ns3:dyDescent="0.2">
+    <row r="28" spans="1:24" ns2:dyDescent="0.2">
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:24" ns3:dyDescent="0.2">
+    <row r="29" spans="1:24" ns2:dyDescent="0.2">
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:24" ns3:dyDescent="0.2">
+    <row r="30" spans="1:24" ns2:dyDescent="0.2">
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:24" ns3:dyDescent="0.2">
+    <row r="31" spans="1:24" ns2:dyDescent="0.2">
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:24" ns3:dyDescent="0.2">
+    <row r="32" spans="1:24" ns2:dyDescent="0.2">
       <c r="F32" s="1"/>
     </row>
-    <row r="33" spans="6:6" ns3:dyDescent="0.2">
+    <row r="33" spans="6:6" ns2:dyDescent="0.2">
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="6:6" ns3:dyDescent="0.2">
+    <row r="34" spans="6:6" ns2:dyDescent="0.2">
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="6:6" ns3:dyDescent="0.2">
+    <row r="35" spans="6:6" ns2:dyDescent="0.2">
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="6:6" ns3:dyDescent="0.2">
+    <row r="36" spans="6:6" ns2:dyDescent="0.2">
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="6:6" ns3:dyDescent="0.2">
+    <row r="37" spans="6:6" ns2:dyDescent="0.2">
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="6:6" ns3:dyDescent="0.2">
+    <row r="38" spans="6:6" ns2:dyDescent="0.2">
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="6:6" ns3:dyDescent="0.2">
+    <row r="39" spans="6:6" ns2:dyDescent="0.2">
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="6:6" ns3:dyDescent="0.2">
+    <row r="40" spans="6:6" ns2:dyDescent="0.2">
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="6:6" ns3:dyDescent="0.2">
+    <row r="41" spans="6:6" ns2:dyDescent="0.2">
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="6:6" ns3:dyDescent="0.2">
+    <row r="42" spans="6:6" ns2:dyDescent="0.2">
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="6:6" ns3:dyDescent="0.2">
+    <row r="43" spans="6:6" ns2:dyDescent="0.2">
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="6:6" ns3:dyDescent="0.2">
+    <row r="44" spans="6:6" ns2:dyDescent="0.2">
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="6:6" ns3:dyDescent="0.2">
+    <row r="45" spans="6:6" ns2:dyDescent="0.2">
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="6:6" ns3:dyDescent="0.2">
+    <row r="46" spans="6:6" ns2:dyDescent="0.2">
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="6:6" ns3:dyDescent="0.2">
+    <row r="47" spans="6:6" ns2:dyDescent="0.2">
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="6:6" ns3:dyDescent="0.2">
+    <row r="48" spans="6:6" ns2:dyDescent="0.2">
       <c r="F48" s="1"/>
     </row>
-    <row r="49" spans="6:6" ns3:dyDescent="0.2">
+    <row r="49" spans="6:6" ns2:dyDescent="0.2">
       <c r="F49" s="1"/>
     </row>
-    <row r="50" spans="6:6" ns3:dyDescent="0.2">
+    <row r="50" spans="6:6" ns2:dyDescent="0.2">
       <c r="F50" s="1"/>
     </row>
-    <row r="51" spans="6:6" ns3:dyDescent="0.2">
+    <row r="51" spans="6:6" ns2:dyDescent="0.2">
       <c r="F51" s="1"/>
     </row>
-    <row r="52" spans="6:6" ns3:dyDescent="0.2">
+    <row r="52" spans="6:6" ns2:dyDescent="0.2">
       <c r="F52" s="1"/>
     </row>
-    <row r="53" spans="6:6" ns3:dyDescent="0.2">
+    <row r="53" spans="6:6" ns2:dyDescent="0.2">
       <c r="F53" s="1"/>
     </row>
-    <row r="54" spans="6:6" ns3:dyDescent="0.2">
+    <row r="54" spans="6:6" ns2:dyDescent="0.2">
       <c r="F54" s="1"/>
     </row>
-    <row r="55" spans="6:6" ns3:dyDescent="0.2">
+    <row r="55" spans="6:6" ns2:dyDescent="0.2">
       <c r="F55" s="1"/>
     </row>
-    <row r="56" spans="6:6" ns3:dyDescent="0.2">
+    <row r="56" spans="6:6" ns2:dyDescent="0.2">
       <c r="F56" s="1"/>
     </row>
-    <row r="57" spans="6:6" ns3:dyDescent="0.2">
+    <row r="57" spans="6:6" ns2:dyDescent="0.2">
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="6:6" ns3:dyDescent="0.2">
+    <row r="58" spans="6:6" ns2:dyDescent="0.2">
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="6:6" ns3:dyDescent="0.2">
+    <row r="59" spans="6:6" ns2:dyDescent="0.2">
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="6:6" ns3:dyDescent="0.2">
+    <row r="60" spans="6:6" ns2:dyDescent="0.2">
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="6:6" ns3:dyDescent="0.2">
+    <row r="61" spans="6:6" ns2:dyDescent="0.2">
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="6:6" ns3:dyDescent="0.2">
+    <row r="62" spans="6:6" ns2:dyDescent="0.2">
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="6:6" ns3:dyDescent="0.2">
+    <row r="63" spans="6:6" ns2:dyDescent="0.2">
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="6:6" ns3:dyDescent="0.2">
+    <row r="64" spans="6:6" ns2:dyDescent="0.2">
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="6:6" ns3:dyDescent="0.2">
+    <row r="65" spans="6:6" ns2:dyDescent="0.2">
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="6:6" ns3:dyDescent="0.2">
+    <row r="66" spans="6:6" ns2:dyDescent="0.2">
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="6:6" ns3:dyDescent="0.2">
+    <row r="67" spans="6:6" ns2:dyDescent="0.2">
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="6:6" ns3:dyDescent="0.2">
+    <row r="68" spans="6:6" ns2:dyDescent="0.2">
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="6:6" ns3:dyDescent="0.2">
+    <row r="69" spans="6:6" ns2:dyDescent="0.2">
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="6:6" ns3:dyDescent="0.2">
+    <row r="70" spans="6:6" ns2:dyDescent="0.2">
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="6:6" ns3:dyDescent="0.2">
+    <row r="71" spans="6:6" ns2:dyDescent="0.2">
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="6:6" ns3:dyDescent="0.2">
+    <row r="72" spans="6:6" ns2:dyDescent="0.2">
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="6:6" ns3:dyDescent="0.2">
+    <row r="73" spans="6:6" ns2:dyDescent="0.2">
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="6:6" ns3:dyDescent="0.2">
+    <row r="74" spans="6:6" ns2:dyDescent="0.2">
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="6:6" ns3:dyDescent="0.2">
+    <row r="75" spans="6:6" ns2:dyDescent="0.2">
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="6:6" ns3:dyDescent="0.2">
+    <row r="76" spans="6:6" ns2:dyDescent="0.2">
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="6:6" ns3:dyDescent="0.2">
+    <row r="77" spans="6:6" ns2:dyDescent="0.2">
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="6:6" ns3:dyDescent="0.2">
+    <row r="78" spans="6:6" ns2:dyDescent="0.2">
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="6:6" ns3:dyDescent="0.2">
+    <row r="79" spans="6:6" ns2:dyDescent="0.2">
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="6:6" ns3:dyDescent="0.2">
+    <row r="80" spans="6:6" ns2:dyDescent="0.2">
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="6:6" ns3:dyDescent="0.2">
+    <row r="81" spans="6:6" ns2:dyDescent="0.2">
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="6:6" ns3:dyDescent="0.2">
+    <row r="82" spans="6:6" ns2:dyDescent="0.2">
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="6:6" ns3:dyDescent="0.2">
+    <row r="83" spans="6:6" ns2:dyDescent="0.2">
       <c r="F83" s="1"/>
     </row>
-    <row r="84" spans="6:6" ns3:dyDescent="0.2">
+    <row r="84" spans="6:6" ns2:dyDescent="0.2">
       <c r="F84" s="1"/>
     </row>
-    <row r="85" spans="6:6" ns3:dyDescent="0.2">
+    <row r="85" spans="6:6" ns2:dyDescent="0.2">
       <c r="F85" s="1"/>
     </row>
-    <row r="86" spans="6:6" ns3:dyDescent="0.2">
+    <row r="86" spans="6:6" ns2:dyDescent="0.2">
       <c r="F86" s="1"/>
     </row>
-    <row r="87" spans="6:6" ns3:dyDescent="0.2">
+    <row r="87" spans="6:6" ns2:dyDescent="0.2">
       <c r="F87" s="1"/>
     </row>
-    <row r="88" spans="6:6" ns3:dyDescent="0.2">
+    <row r="88" spans="6:6" ns2:dyDescent="0.2">
       <c r="F88" s="1"/>
     </row>
-    <row r="89" spans="6:6" ns3:dyDescent="0.2">
+    <row r="89" spans="6:6" ns2:dyDescent="0.2">
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="6:6" ns3:dyDescent="0.2">
+    <row r="90" spans="6:6" ns2:dyDescent="0.2">
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="6:6" ns3:dyDescent="0.2">
+    <row r="91" spans="6:6" ns2:dyDescent="0.2">
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="6:6" ns3:dyDescent="0.2">
+    <row r="92" spans="6:6" ns2:dyDescent="0.2">
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="6:6" ns3:dyDescent="0.2">
+    <row r="93" spans="6:6" ns2:dyDescent="0.2">
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="6:6" ns3:dyDescent="0.2">
+    <row r="94" spans="6:6" ns2:dyDescent="0.2">
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="6:6" ns3:dyDescent="0.2">
+    <row r="95" spans="6:6" ns2:dyDescent="0.2">
       <c r="F95" s="1"/>
     </row>
-    <row r="96" spans="6:6" ns3:dyDescent="0.2">
+    <row r="96" spans="6:6" ns2:dyDescent="0.2">
       <c r="F96" s="1"/>
     </row>
-    <row r="97" spans="6:6" ns3:dyDescent="0.2">
+    <row r="97" spans="6:6" ns2:dyDescent="0.2">
       <c r="F97" s="1"/>
     </row>
-    <row r="98" spans="6:6" ns3:dyDescent="0.2">
+    <row r="98" spans="6:6" ns2:dyDescent="0.2">
       <c r="F98" s="1"/>
     </row>
-    <row r="99" spans="6:6" ns3:dyDescent="0.2">
+    <row r="99" spans="6:6" ns2:dyDescent="0.2">
       <c r="F99" s="1"/>
     </row>
-    <row r="100" spans="6:6" ns3:dyDescent="0.2">
+    <row r="100" spans="6:6" ns2:dyDescent="0.2">
       <c r="F100" s="1"/>
     </row>
-    <row r="101" spans="6:6" ns3:dyDescent="0.2">
+    <row r="101" spans="6:6" ns2:dyDescent="0.2">
       <c r="F101" s="1"/>
     </row>
-    <row r="102" spans="6:6" ns3:dyDescent="0.2">
+    <row r="102" spans="6:6" ns2:dyDescent="0.2">
       <c r="F102" s="1"/>
     </row>
-    <row r="103" spans="6:6" ns3:dyDescent="0.2">
+    <row r="103" spans="6:6" ns2:dyDescent="0.2">
       <c r="F103" s="1"/>
     </row>
-    <row r="104" spans="6:6" ns3:dyDescent="0.2">
+    <row r="104" spans="6:6" ns2:dyDescent="0.2">
       <c r="F104" s="1"/>
     </row>
-    <row r="105" spans="6:6" ns3:dyDescent="0.2">
+    <row r="105" spans="6:6" ns2:dyDescent="0.2">
       <c r="F105" s="1"/>
     </row>
-    <row r="106" spans="6:6" ns3:dyDescent="0.2">
+    <row r="106" spans="6:6" ns2:dyDescent="0.2">
       <c r="F106" s="1"/>
     </row>
-    <row r="107" spans="6:6" ns3:dyDescent="0.2">
+    <row r="107" spans="6:6" ns2:dyDescent="0.2">
       <c r="F107" s="1"/>
     </row>
-    <row r="108" spans="6:6" ns3:dyDescent="0.2">
+    <row r="108" spans="6:6" ns2:dyDescent="0.2">
       <c r="F108" s="1"/>
     </row>
-    <row r="109" spans="6:6" ns3:dyDescent="0.2">
+    <row r="109" spans="6:6" ns2:dyDescent="0.2">
       <c r="F109" s="1"/>
     </row>
-    <row r="110" spans="6:6" ns3:dyDescent="0.2">
+    <row r="110" spans="6:6" ns2:dyDescent="0.2">
       <c r="F110" s="1"/>
     </row>
-    <row r="111" spans="6:6" ns3:dyDescent="0.2">
+    <row r="111" spans="6:6" ns2:dyDescent="0.2">
       <c r="F111" s="1"/>
     </row>
-    <row r="112" spans="6:6" ns3:dyDescent="0.2">
+    <row r="112" spans="6:6" ns2:dyDescent="0.2">
       <c r="F112" s="1"/>
     </row>
-    <row r="113" spans="6:6" ns3:dyDescent="0.2">
+    <row r="113" spans="6:6" ns2:dyDescent="0.2">
       <c r="F113" s="1"/>
     </row>
-    <row r="114" spans="6:6" ns3:dyDescent="0.2">
+    <row r="114" spans="6:6" ns2:dyDescent="0.2">
       <c r="F114" s="1"/>
     </row>
-    <row r="115" spans="6:6" ns3:dyDescent="0.2">
+    <row r="115" spans="6:6" ns2:dyDescent="0.2">
       <c r="F115" s="1"/>
     </row>
-    <row r="116" spans="6:6" ns3:dyDescent="0.2">
+    <row r="116" spans="6:6" ns2:dyDescent="0.2">
       <c r="F116" s="1"/>
     </row>
-    <row r="117" spans="6:6" ns3:dyDescent="0.2">
+    <row r="117" spans="6:6" ns2:dyDescent="0.2">
       <c r="F117" s="1"/>
     </row>
-    <row r="118" spans="6:6" ns3:dyDescent="0.2">
+    <row r="118" spans="6:6" ns2:dyDescent="0.2">
       <c r="F118" s="1"/>
     </row>
-    <row r="119" spans="6:6" ns3:dyDescent="0.2">
+    <row r="119" spans="6:6" ns2:dyDescent="0.2">
       <c r="F119" s="1"/>
     </row>
-    <row r="120" spans="6:6" ns3:dyDescent="0.2">
+    <row r="120" spans="6:6" ns2:dyDescent="0.2">
       <c r="F120" s="1"/>
     </row>
-    <row r="121" spans="6:6" ns3:dyDescent="0.2">
+    <row r="121" spans="6:6" ns2:dyDescent="0.2">
       <c r="F121" s="1"/>
     </row>
-    <row r="122" spans="6:6" ns3:dyDescent="0.2">
+    <row r="122" spans="6:6" ns2:dyDescent="0.2">
       <c r="F122" s="1"/>
     </row>
-    <row r="123" spans="6:6" ns3:dyDescent="0.2">
+    <row r="123" spans="6:6" ns2:dyDescent="0.2">
       <c r="F123" s="1"/>
     </row>
-    <row r="124" spans="6:6" ns3:dyDescent="0.2">
+    <row r="124" spans="6:6" ns2:dyDescent="0.2">
       <c r="F124" s="1"/>
     </row>
-    <row r="125" spans="6:6" ns3:dyDescent="0.2">
+    <row r="125" spans="6:6" ns2:dyDescent="0.2">
       <c r="F125" s="1"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="21">
+  <mergeCells count="30">
     <mergeCell ref="A22:B23"/>
     <mergeCell ref="Q22:R23"/>
-    <mergeCell ref="K1:V1"/>
     <mergeCell ref="J19:K20"/>
     <mergeCell ref="T6:T7"/>
     <mergeCell ref="S6:S7"/>
@@ -3193,13 +4645,23 @@
     <mergeCell ref="Q19:R20"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E10:F10"/>
-    <mergeCell ref="K3:O3"/>
     <mergeCell ref="A17:B18"/>
     <mergeCell ref="C17:D18"/>
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="L17:P18"/>
     <mergeCell ref="J17:K18"/>
     <mergeCell ref="Q17:R18"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:V2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:V3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:V4"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:D8">
     <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">
@@ -3217,24 +4679,21 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" ns2:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" ns2:uid="{00000000-0002-0000-0000-000001000000}"/>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="G16 H11:H13" ns2:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" ns1:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" ns1:uid="{00000000-0002-0000-0000-000001000000}"/>
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="G16 H11:H13" ns1:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" ns2:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" ns1:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="A3" ns4:id="rId1" display="www.federation.org" ns2:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A4" ns4:id="rId2" display="records@federation.org" ns2:uid="{00000000-0004-0000-0000-000001000000}"/>
-  </hyperlinks>
+  <hyperlinks/>
   <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="71" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns4:id="rId3"/>
+  <pageSetup paperSize="9" scale="71" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns3:id="rId3"/>
   <headerFooter alignWithMargins="0"/>
-  <legacyDrawing ns4:id="rId4"/>
+  <legacyDrawing ns3:id="rId4"/>
 </worksheet>
 </file>